--- a/xlsx/EIGO_NO_PARTNERに出てくる文.xlsx
+++ b/xlsx/EIGO_NO_PARTNERに出てくる文.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\payor\Desktop\TranslationTest\translation-test-app\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\payor\Desktop\稼働中プロジェクト\Devcontainer使用プロジェクト\コンテナあり\EnglishTest_Devcon\english-test-app\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3AE978-8A66-4C8B-B9C4-97FFDF28D535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6897DE2B-70F9-496D-AD10-23C0BE2AC773}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="825">
   <si>
     <t>Lesson</t>
   </si>
@@ -2388,6 +2388,343 @@
   </si>
   <si>
     <t>私はミカです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I go to Okinawa every summer.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は毎年夏に沖縄に行きます。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マイトシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>オキナワ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I went to Okinawa last summer.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は昨年の夏に沖縄に行きました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクネン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>オキナワ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I enjoy swimming.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は水泳を楽しみます。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>スイエイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I enjoyed swimming.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は水泳を楽しみました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>スイエイ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>タノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I went to the sea last Sunday.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私はこの前の日曜日、海に行きました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ニチヨウビ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ウミ</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I enjoyed the summer festival this year.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は今年、夏祭りを楽しみました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>コトシ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ナツマツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タノ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I ate curry last weekend.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は先週末、カレーを食べました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>センシュウマツ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I saw lots of people at the station.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は駅でたくさんの人を見ました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>エキ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I went to the library last Sunday.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私はこの前の日曜日、図書館に行きました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>ニチヨウビ</t>
+    </rPh>
+    <rPh sb="10" eb="13">
+      <t>トショカン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I ate grilled fish last night.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は昨晩、焼き魚を食べました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクバン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ヤ</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>ザカナ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>タ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I saw Mika last weekend.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は先週末、ミカに会いました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>センシュウマツ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>The curry was delicious.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>そのカレーはおいしかったです。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>family</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>家族</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>view</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>景色、ながめ</t>
+    <rPh sb="0" eb="2">
+      <t>ケシキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>thick</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>分厚い</t>
+    <rPh sb="0" eb="2">
+      <t>ブアツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>year</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>年、1年</t>
+    <rPh sb="0" eb="1">
+      <t>ネン</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>also</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>…もまた</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>top</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>頂上</t>
+    <rPh sb="0" eb="2">
+      <t>チョウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I saw fireworks last summer.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は昨年の夏、花火を見ました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクネン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ナツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ハナビ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ミ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>I went to Tokyo by myself.</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>私は独力で東京に行きました。</t>
+    <rPh sb="0" eb="1">
+      <t>ワタシ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ドクリョク</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>トウキョウ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>イ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -2557,7 +2894,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2595,6 +2932,15 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -2929,7 +3275,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D399"/>
+  <dimension ref="A1:D419"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="21" style="12" customWidth="1"/>
@@ -8507,6 +8853,286 @@
         <v>783</v>
       </c>
     </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A400" s="13">
+        <v>4</v>
+      </c>
+      <c r="B400" s="12">
+        <v>1</v>
+      </c>
+      <c r="C400" s="14" t="s">
+        <v>785</v>
+      </c>
+      <c r="D400" s="15" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A401" s="13">
+        <v>4</v>
+      </c>
+      <c r="B401" s="12">
+        <v>1</v>
+      </c>
+      <c r="C401" s="14" t="s">
+        <v>787</v>
+      </c>
+      <c r="D401" s="15" t="s">
+        <v>788</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A402" s="13">
+        <v>4</v>
+      </c>
+      <c r="B402" s="12">
+        <v>1</v>
+      </c>
+      <c r="C402" s="14" t="s">
+        <v>789</v>
+      </c>
+      <c r="D402" s="15" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A403" s="13">
+        <v>4</v>
+      </c>
+      <c r="B403" s="12">
+        <v>1</v>
+      </c>
+      <c r="C403" s="14" t="s">
+        <v>791</v>
+      </c>
+      <c r="D403" s="15" t="s">
+        <v>792</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A404" s="13">
+        <v>4</v>
+      </c>
+      <c r="B404" s="12">
+        <v>1</v>
+      </c>
+      <c r="C404" s="14" t="s">
+        <v>793</v>
+      </c>
+      <c r="D404" s="15" t="s">
+        <v>794</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A405" s="13">
+        <v>4</v>
+      </c>
+      <c r="B405" s="12">
+        <v>1</v>
+      </c>
+      <c r="C405" s="14" t="s">
+        <v>795</v>
+      </c>
+      <c r="D405" s="15" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A406" s="13">
+        <v>4</v>
+      </c>
+      <c r="B406" s="12">
+        <v>1</v>
+      </c>
+      <c r="C406" s="14" t="s">
+        <v>797</v>
+      </c>
+      <c r="D406" s="15" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A407" s="13">
+        <v>4</v>
+      </c>
+      <c r="B407" s="12">
+        <v>1</v>
+      </c>
+      <c r="C407" s="14" t="s">
+        <v>799</v>
+      </c>
+      <c r="D407" s="15" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A408" s="13">
+        <v>4</v>
+      </c>
+      <c r="B408" s="12">
+        <v>1</v>
+      </c>
+      <c r="C408" s="14" t="s">
+        <v>801</v>
+      </c>
+      <c r="D408" s="15" t="s">
+        <v>802</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A409" s="13">
+        <v>4</v>
+      </c>
+      <c r="B409" s="12">
+        <v>1</v>
+      </c>
+      <c r="C409" s="14" t="s">
+        <v>803</v>
+      </c>
+      <c r="D409" s="15" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A410" s="13">
+        <v>4</v>
+      </c>
+      <c r="B410" s="12">
+        <v>1</v>
+      </c>
+      <c r="C410" s="14" t="s">
+        <v>805</v>
+      </c>
+      <c r="D410" s="15" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A411" s="13">
+        <v>4</v>
+      </c>
+      <c r="B411" s="12">
+        <v>1</v>
+      </c>
+      <c r="C411" s="14" t="s">
+        <v>807</v>
+      </c>
+      <c r="D411" s="15" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A412" s="13">
+        <v>4</v>
+      </c>
+      <c r="B412" s="12">
+        <v>1</v>
+      </c>
+      <c r="C412" s="14" t="s">
+        <v>809</v>
+      </c>
+      <c r="D412" s="15" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A413" s="13">
+        <v>4</v>
+      </c>
+      <c r="B413" s="12">
+        <v>1</v>
+      </c>
+      <c r="C413" s="14" t="s">
+        <v>811</v>
+      </c>
+      <c r="D413" s="15" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A414" s="13">
+        <v>4</v>
+      </c>
+      <c r="B414" s="12">
+        <v>1</v>
+      </c>
+      <c r="C414" s="14" t="s">
+        <v>819</v>
+      </c>
+      <c r="D414" s="15" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A415" s="13">
+        <v>4</v>
+      </c>
+      <c r="B415" s="12">
+        <v>1</v>
+      </c>
+      <c r="C415" s="14" t="s">
+        <v>813</v>
+      </c>
+      <c r="D415" s="15" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A416" s="13">
+        <v>4</v>
+      </c>
+      <c r="B416" s="12">
+        <v>1</v>
+      </c>
+      <c r="C416" s="14" t="s">
+        <v>815</v>
+      </c>
+      <c r="D416" s="15" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A417" s="13">
+        <v>4</v>
+      </c>
+      <c r="B417" s="12">
+        <v>1</v>
+      </c>
+      <c r="C417" s="14" t="s">
+        <v>817</v>
+      </c>
+      <c r="D417" s="15" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A418" s="13">
+        <v>4</v>
+      </c>
+      <c r="B418" s="12">
+        <v>1</v>
+      </c>
+      <c r="C418" s="14" t="s">
+        <v>821</v>
+      </c>
+      <c r="D418" s="15" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A419" s="13">
+        <v>4</v>
+      </c>
+      <c r="B419" s="12">
+        <v>1</v>
+      </c>
+      <c r="C419" s="14" t="s">
+        <v>823</v>
+      </c>
+      <c r="D419" s="15" t="s">
+        <v>824</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
